--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_82_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_82_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1805</v>
+        <v>5.5178</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7091</v>
+        <v>5.1809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4714</v>
+        <v>0.3369</v>
       </c>
       <c r="G2" t="n">
         <v>3.5361</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1237</v>
+        <v>-0.7863</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2275</v>
+        <v>-0.362</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4126</v>
+        <v>3.3803</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0152</v>
+        <v>-0.5434</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4277</v>
+        <v>3.9236</v>
       </c>
       <c r="G3" t="n">
         <v>1.678</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1753</v>
+        <v>-0.2076</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7209</v>
+        <v>0.2168</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7393</v>
+        <v>2.5445</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4733</v>
+        <v>0.3121</v>
       </c>
       <c r="F4" t="n">
-        <v>2.266</v>
+        <v>2.2324</v>
       </c>
       <c r="G4" t="n">
         <v>3.1872</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5021</v>
+        <v>-0.6969</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2592</v>
+        <v>-0.4204</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2429</v>
+        <v>-0.2765</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.413</v>
+        <v>2.3685</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2289</v>
+        <v>1.1091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1841</v>
+        <v>1.2594</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3089</v>
+        <v>2.4609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6062</v>
+        <v>1.3133</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7027</v>
+        <v>1.1476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8802</v>
+        <v>1.4284</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8066</v>
+        <v>1.4319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>-0.0035</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4287</v>
+        <v>1.0325</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2004</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6291</v>
+        <v>1.1511</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4598</v>
+        <v>-0.7883</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3486</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1111</v>
+        <v>-0.5566</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8197</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1295</v>
+        <v>2.2131</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0232</v>
+        <v>1.9052</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1063</v>
+        <v>0.3079</v>
       </c>
       <c r="G6" t="n">
         <v>1.585</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.007</v>
+        <v>0.0767</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.295</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2892</v>
+        <v>1.5537</v>
       </c>
       <c r="E7" t="n">
-        <v>0.739</v>
+        <v>1.4032</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5502</v>
+        <v>0.1505</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1145</v>
+        <v>1.3089</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3554</v>
+        <v>0.6062</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2409</v>
+        <v>0.7027</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4754</v>
+        <v>0.8802</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.8066</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3914</v>
+        <v>0.0736</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3609</v>
+        <v>0.4287</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2714</v>
+        <v>-0.2004</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6323</v>
+        <v>0.6291</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2469</v>
+        <v>0.6005</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.523</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0167</v>
+        <v>0.0775</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2335</v>
+        <v>0.7337</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4447</v>
+        <v>0.3852</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7889</v>
+        <v>0.3485</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4609</v>
+        <v>0.1145</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3133</v>
+        <v>0.3554</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1476</v>
+        <v>-0.2409</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4284</v>
+        <v>0.4754</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4319</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0035</v>
+        <v>0.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0325</v>
+        <v>-0.3609</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1186</v>
+        <v>0.2714</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1511</v>
+        <v>-0.6323</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9233</v>
+        <v>-0.3086</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0271</v>
+        <v>-0.2183</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9802</v>
+        <v>-0.1986</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8856000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0946</v>
+        <v>-0.1407</v>
       </c>
       <c r="G9" t="n">
         <v>0.3566</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3763</v>
+        <v>0.1975</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8259</v>
+        <v>-0.1177</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5505</v>
+        <v>0.3152</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0626</v>
+        <v>-0.4831</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7469</v>
+        <v>-1.4363</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6843</v>
+        <v>0.9532</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1804</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.346</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8962</v>
+        <v>-0.5856</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4498</v>
+        <v>-0.181</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3841</v>
+        <v>-0.7533</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2752</v>
+        <v>1.9396</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6593</v>
+        <v>-2.6929</v>
       </c>
       <c r="G12" t="n">
         <v>1.574</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1901</v>
+        <v>-0.5592</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>-0.3064</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2192</v>
+        <v>-0.2528</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3802</v>
+        <v>-2.9523</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8769</v>
+        <v>-2.6843</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5033</v>
+        <v>-0.268</v>
       </c>
       <c r="G13" t="n">
         <v>0.2948</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5153</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1142</v>
+        <v>0.3068</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.3082</v>
+        <v>13.6816</v>
       </c>
       <c r="E14" t="n">
-        <v>7.065300000000001</v>
+        <v>7.438600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>6.2429</v>
+        <v>6.242800000000003</v>
       </c>
       <c r="G14" t="n">
         <v>15.9048</v>
@@ -1516,7 +1516,7 @@
         <v>9.597800000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>6.307200000000001</v>
+        <v>6.307200000000002</v>
       </c>
       <c r="J14" t="n">
         <v>15.0302</v>
@@ -1546,22 +1546,22 @@
         <v>16.2367</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.9318</v>
+        <v>-3.5582</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9244</v>
+        <v>-1.5508</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.0075</v>
+        <v>-2.0076</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1444</v>
       </c>
       <c r="W14" t="n">
-        <v>6.716800000000001</v>
+        <v>6.7168</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.8612</v>
+        <v>-8.861200000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.860300000000001</v>
+        <v>7.6719</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2553</v>
+        <v>5.8399</v>
       </c>
       <c r="F15" t="n">
-        <v>2.605</v>
+        <v>1.832</v>
       </c>
       <c r="G15" t="n">
         <v>2.5282</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7934</v>
+        <v>1.605</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1903</v>
+        <v>0.7749</v>
       </c>
       <c r="U15" t="n">
-        <v>1.603</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>3.0748</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1297</v>
+        <v>0.9012</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9679</v>
+        <v>2.2095</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-1.3083</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0508</v>
+        <v>0.5984</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1043</v>
+        <v>-1.3289</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0535</v>
+        <v>1.9273</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7765</v>
+        <v>2.0639</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7765</v>
+        <v>-0.131</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.1949</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7257</v>
+        <v>-1.4655</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6722</v>
+        <v>-1.1979</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0535</v>
+        <v>-0.2676</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3109</v>
+        <v>0.6792</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4233</v>
+        <v>0.3776</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1125</v>
+        <v>0.3016</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6044</v>
+        <v>0.8408</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1852</v>
+        <v>3.1221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7896</v>
+        <v>-2.2813</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.031</v>
+        <v>0.795</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0301</v>
+        <v>-0.9316</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0611</v>
+        <v>1.7266</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5551</v>
+        <v>2.8256</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.0958</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6391</v>
+        <v>1.7298</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4759</v>
+        <v>-2.0306</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0539</v>
+        <v>-2.0274</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.422</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7076</v>
+        <v>0.3499</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0657</v>
+        <v>-0.0077</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6418</v>
+        <v>0.3576</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5198</v>
+        <v>0.4452</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5323</v>
+        <v>-0.4731</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0125</v>
+        <v>0.9183</v>
       </c>
       <c r="G18" t="n">
-        <v>0.795</v>
+        <v>-3.6202</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9316</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7266</v>
+        <v>-2.7739</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8256</v>
+        <v>-3.1303</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0958</v>
+        <v>-0.4131</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7298</v>
+        <v>-2.7172</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0306</v>
+        <v>-0.4899</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0274</v>
+        <v>-0.4331</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0033</v>
+        <v>-0.0568</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.029</v>
+        <v>0.4571</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>0.2087</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6264</v>
+        <v>0.2484</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.2533</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.709</v>
+        <v>1.0243</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6158</v>
+        <v>-0.771</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6202</v>
+        <v>0.0508</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0.1043</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7739</v>
+        <v>-0.0535</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1303</v>
+        <v>0.7765</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4131</v>
+        <v>0.7765</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.7172</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4899</v>
+        <v>-0.7257</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4331</v>
+        <v>-0.6722</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0568</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0813</v>
+        <v>0.4345</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0272</v>
+        <v>0.4797</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.054</v>
+        <v>-0.0452</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2941</v>
+        <v>-0.2549</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3839</v>
+        <v>-1.0109</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.678</v>
+        <v>0.756</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5984</v>
+        <v>-2.031</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3289</v>
+        <v>0.0301</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9273</v>
+        <v>-2.0611</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0639</v>
+        <v>-0.5551</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.131</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1949</v>
+        <v>-0.6391</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4655</v>
+        <v>-1.4759</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1979</v>
+        <v>-0.0539</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2676</v>
+        <v>-1.422</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5162</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4481</v>
+        <v>0.2401</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. TAYLOR</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5465</v>
+        <v>-0.2847</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0104</v>
+        <v>1.1203</v>
       </c>
       <c r="F21" t="n">
+        <v>-1.405</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.3531</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1.2713</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.1049</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.458</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.529</v>
+      </c>
+      <c r="P21" t="n">
         <v>0.4639</v>
       </c>
-      <c r="G21" t="n">
-        <v>-0.7863</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.7863</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.7863</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.7863</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.232</v>
-      </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.3932</v>
       </c>
       <c r="T21" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.2833</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>B. TAYLOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7894</v>
+        <v>-0.4285</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8844</v>
+        <v>-0.8924</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6738</v>
+        <v>0.4639</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3531</v>
+        <v>-0.7863</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9182</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2713</v>
+        <v>-0.7863</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1049</v>
+        <v>-0.7863</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8472</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2576</v>
+        <v>-0.7863</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.458</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.529</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.4639</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.6237</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.0876</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.1116</v>
+        <v>0.1259</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0474</v>
+        <v>0.1259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.159</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9931</v>
+        <v>-2.1117</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8981</v>
+        <v>-1.2519</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.095</v>
+        <v>-0.8597</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5421</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5232</v>
+        <v>-0.6418</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5515</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2277</v>
+        <v>-4.7565</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2949</v>
+        <v>-3.059</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9327</v>
+        <v>-1.6975</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6323</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2191</v>
+        <v>-0.7479</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>-0.4283</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5548</v>
+        <v>-0.3196</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3693</v>
+        <v>-6.2678</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0142</v>
+        <v>-3.7783</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3551</v>
+        <v>-2.4895</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6557</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1801</v>
+        <v>-0.0786</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3655</v>
+        <v>-0.1296</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1854</v>
+        <v>0.051</v>
       </c>
       <c r="V25" t="n">
         <v>-1.214</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.1091</v>
+        <v>-9.3164</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.1547</v>
+        <v>-9.0931</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0456</v>
+        <v>-0.2233</v>
       </c>
       <c r="G26" t="n">
         <v>-6.2568</v>
@@ -2482,13 +2482,13 @@
         <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2855</v>
+        <v>0.5072</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8883</v>
+        <v>0.1733</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6027</v>
+        <v>0.3339</v>
       </c>
       <c r="V26" t="n">
         <v>1.0722</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.3082</v>
+        <v>-13.3081</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.2427</v>
+        <v>-6.242600000000001</v>
       </c>
       <c r="F27" t="n">
         <v>-7.0654</v>
@@ -2530,13 +2530,13 @@
         <v>-9.597999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.306999999999999</v>
+        <v>-6.307</v>
       </c>
       <c r="J27" t="n">
         <v>-0.8749999999999996</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.229200000000001</v>
+        <v>-2.2292</v>
       </c>
       <c r="L27" t="n">
         <v>1.3542</v>
@@ -2560,13 +2560,13 @@
         <v>12.7575</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9318</v>
+        <v>3.932</v>
       </c>
       <c r="T27" t="n">
-        <v>2.0074</v>
+        <v>2.0076</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9241</v>
+        <v>1.9243</v>
       </c>
       <c r="V27" t="n">
         <v>2.144400000000001</v>
